--- a/results/excel_reports/independent_vgg16_random_noise.xlsx
+++ b/results/excel_reports/independent_vgg16_random_noise.xlsx
@@ -1136,7 +1136,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -1236,7 +1236,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8178178178178178</v>
       </c>
       <c r="C2" t="n">
         <v>0.78</v>
@@ -1306,7 +1306,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8178178178178178</v>
       </c>
       <c r="C3" t="n">
         <v>0.789</v>
@@ -1376,7 +1376,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8178178178178178</v>
       </c>
       <c r="C4" t="n">
         <v>0.788</v>
@@ -1446,7 +1446,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8178178178178178</v>
       </c>
       <c r="C5" t="n">
         <v>0.787</v>
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8178178178178178</v>
       </c>
       <c r="C6" t="n">
         <v>0.794</v>
@@ -1586,7 +1586,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8178178178178178</v>
       </c>
       <c r="C7" t="n">
         <v>0.78</v>
@@ -1656,7 +1656,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.8178178178178178</v>
       </c>
       <c r="C8" t="n">
         <v>0.805</v>
@@ -1747,7 +1747,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="7" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
@@ -1847,7 +1847,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.952</v>
+        <v>0.9519519519519519</v>
       </c>
       <c r="C2" t="n">
         <v>0.9419999999999999</v>
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.952</v>
+        <v>0.9519519519519519</v>
       </c>
       <c r="C3" t="n">
         <v>0.9370000000000001</v>
@@ -1987,7 +1987,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.952</v>
+        <v>0.9519519519519519</v>
       </c>
       <c r="C4" t="n">
         <v>0.9419999999999999</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.952</v>
+        <v>0.9519519519519519</v>
       </c>
       <c r="C5" t="n">
         <v>0.9429999999999999</v>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.952</v>
+        <v>0.9519519519519519</v>
       </c>
       <c r="C6" t="n">
         <v>0.946</v>
@@ -2197,7 +2197,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.952</v>
+        <v>0.9519519519519519</v>
       </c>
       <c r="C7" t="n">
         <v>0.9419999999999999</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.952</v>
+        <v>0.9519519519519519</v>
       </c>
       <c r="C8" t="n">
         <v>0.9399999999999999</v>
